--- a/medical_surveys_questionnaires/014_cardiovascular_system_assessment--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/014_cardiovascular_system_assessment--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -916,8 +916,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -945,12 +945,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'palpitations',_'value':_'palpitations'}</t>
+          <t>palpitations</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Palpitations', 'value': 'palpitations'}</t>
+          <t>Palpitations</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'syncope',_'value':_'syncope'}</t>
+          <t>syncope</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Syncope', 'value': 'syncope'}</t>
+          <t>Syncope</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'orthopnea',_'value':_'orthopnea'}</t>
+          <t>orthopnea</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Orthopnea', 'value': 'orthopnea'}</t>
+          <t>Orthopnea</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'paroxysmal_nocturnal_dyspnea',_'value':_'pnd'}</t>
+          <t>paroxysmal_nocturnal_dyspnea</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Paroxysmal Nocturnal Dyspnea', 'value': 'pnd'}</t>
+          <t>Paroxysmal Nocturnal Dyspnea</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'fatigue',_'value':_'fatigue'}</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Fatigue', 'value': 'fatigue'}</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'normal_s1/s2',_'value':_'normal'}</t>
+          <t>normal_s1/s2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Normal S1/S2', 'value': 'normal'}</t>
+          <t>Normal S1/S2</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'abnormal_heart_sounds',_'value':_'abnormal'}</t>
+          <t>abnormal_heart_sounds</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Abnormal Heart Sounds', 'value': 'abnormal'}</t>
+          <t>Abnormal Heart Sounds</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'murmur_detected',_'value':_'murmur'}</t>
+          <t>murmur_detected</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Murmur Detected', 'value': 'murmur'}</t>
+          <t>Murmur Detected</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'distant_heart_sounds',_'value':_'distant'}</t>
+          <t>distant_heart_sounds</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Distant Heart Sounds', 'value': 'distant'}</t>
+          <t>Distant Heart Sounds</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'normal/equal_(+2)',_'value':_'normal'}</t>
+          <t>normal/equal_(+2)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Normal/Equal (+2)', 'value': 'normal'}</t>
+          <t>Normal/Equal (+2)</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'diminished/weak_(+1)',_'value':_'weak'}</t>
+          <t>diminished/weak_(+1)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Diminished/Weak (+1)', 'value': 'weak'}</t>
+          <t>Diminished/Weak (+1)</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'absent_(0)',_'value':_'absent'}</t>
+          <t>absent_(0)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Absent (0)', 'value': 'absent'}</t>
+          <t>Absent (0)</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'bounding_(+3)',_'value':_'bounding'}</t>
+          <t>bounding_(+3)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Bounding (+3)', 'value': 'bounding'}</t>
+          <t>Bounding (+3)</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'absent_(no_swelling)',_'value':_'none'}</t>
+          <t>absent_(no_swelling)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Absent (No Swelling)', 'value': 'none'}</t>
+          <t>Absent (No Swelling)</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'pitting_edema_(mild)',_'value':_'pitting_mild'}</t>
+          <t>pitting_edema_(mild)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Pitting Edema (Mild)', 'value': 'pitting_mild'}</t>
+          <t>Pitting Edema (Mild)</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'pitting_edema_(severe)',_'value':_'pitting_severe'}</t>
+          <t>pitting_edema_(severe)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Pitting Edema (Severe)', 'value': 'pitting_severe'}</t>
+          <t>Pitting Edema (Severe)</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'non-pitting_edema',_'value':_'non_pitting'}</t>
+          <t>non-pitting_edema</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Non-Pitting Edema', 'value': 'non_pitting'}</t>
+          <t>Non-Pitting Edema</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'absent',_'value':_'absent'}</t>
+          <t>absent</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Absent', 'value': 'absent'}</t>
+          <t>Absent</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'present',_'value':_'present'}</t>
+          <t>present</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Present', 'value': 'present'}</t>
+          <t>Present</t>
         </is>
       </c>
     </row>
